--- a/Delay Discounting_RashmitaGanguly_AU2320074_Analysis File.xlsx
+++ b/Delay Discounting_RashmitaGanguly_AU2320074_Analysis File.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="18">
   <si>
     <t>reward_today</t>
   </si>
@@ -51,6 +51,12 @@
   </si>
   <si>
     <t>Discounting Values</t>
+  </si>
+  <si>
+    <t>Participants</t>
+  </si>
+  <si>
+    <t>Discounting Value</t>
   </si>
   <si>
     <t>Participant 1</t>
@@ -92,7 +98,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,6 +119,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor rgb="FFF9CB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD0E0E3"/>
         <bgColor rgb="FFD0E0E3"/>
       </patternFill>
@@ -124,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -144,12 +156,87 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="4" pivot="0" name="Overall-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -171,6 +258,16 @@
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A3:B7" displayName="Table1" name="Table1" id="1">
+  <tableColumns count="2">
+    <tableColumn name="Participants" id="1"/>
+    <tableColumn name="Discounting Value" id="2"/>
+  </tableColumns>
+  <tableStyleInfo name="Overall-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1482,8 +1579,7 @@
         <v>9</v>
       </c>
       <c r="H43" s="8">
-        <f>average(E2:E101)</f>
-        <v>0.04875800789</v>
+        <v>0.04875800789176675</v>
       </c>
     </row>
     <row r="44">
@@ -2588,12 +2684,21 @@
         <f t="shared" ref="E2:E101" si="1">((B2/A2)-1)/C2</f>
         <v>0.001011889704</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.20526315789473687</v>
+      </c>
+      <c r="I2" s="6">
+        <f>geomean(H2:H3)</f>
+        <v>0.07307966043</v>
+      </c>
       <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L2" s="8">
-        <f>average(E2:E101)</f>
-        <v>0.04875800789</v>
+        <v>0.04875800789176675</v>
       </c>
     </row>
     <row r="3">
@@ -2613,6 +2718,12 @@
         <f t="shared" si="1"/>
         <v>0.007738206228</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.026018486819582333</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
@@ -2631,6 +2742,16 @@
         <f t="shared" si="1"/>
         <v>0.02565298507</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.16296296296296298</v>
+      </c>
+      <c r="I4" s="6">
+        <f>geomean(H4:H5)</f>
+        <v>0.06157233359</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
@@ -2649,6 +2770,12 @@
         <f t="shared" si="1"/>
         <v>0.03195352215</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.02326388888888889</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
@@ -2667,6 +2794,16 @@
         <f t="shared" si="1"/>
         <v>0.03175675676</v>
       </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.012089810017271158</v>
+      </c>
+      <c r="I6" s="6">
+        <f>geomean(H6:H7)</f>
+        <v>0.005725115042</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
@@ -2685,6 +2822,12 @@
         <f t="shared" si="1"/>
         <v>0.02019906323</v>
       </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.0027111213659437015</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
@@ -2750,10 +2893,10 @@
       <c r="C11" s="3">
         <v>10.0</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="10">
         <f t="shared" si="1"/>
         <v>0.2052631579</v>
       </c>
@@ -2768,10 +2911,10 @@
       <c r="C12" s="3">
         <v>127.0</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="D12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="10">
         <f t="shared" si="1"/>
         <v>0.02601848682</v>
       </c>
@@ -3884,10 +4027,10 @@
       <c r="C74" s="3">
         <v>30.0</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="6">
+      <c r="D74" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="10">
         <f t="shared" si="1"/>
         <v>0.162962963</v>
       </c>
@@ -3902,10 +4045,10 @@
       <c r="C75" s="3">
         <v>45.0</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="6">
+      <c r="D75" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="10">
         <f t="shared" si="1"/>
         <v>0.02326388889</v>
       </c>
@@ -3920,10 +4063,10 @@
       <c r="C76" s="3">
         <v>193.0</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="6">
+      <c r="D76" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="10">
         <f t="shared" si="1"/>
         <v>0.01208981002</v>
       </c>
@@ -3938,10 +4081,10 @@
       <c r="C77" s="3">
         <v>197.0</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="6">
+      <c r="D77" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="10">
         <f t="shared" si="1"/>
         <v>0.002711121366</v>
       </c>
@@ -4436,12 +4579,21 @@
         <f t="shared" ref="E2:E101" si="1">((B2/A2)-1)/C2</f>
         <v>0.01276742581</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.023420479302832243</v>
+      </c>
+      <c r="I2" s="6">
+        <f>geomean(H2:H3)</f>
+        <v>0.01870834298</v>
+      </c>
       <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L2" s="8">
-        <f>average(E2:E101)</f>
-        <v>0.04875800789</v>
+        <v>0.04875800789176675</v>
       </c>
     </row>
     <row r="3">
@@ -4461,6 +4613,12 @@
         <f t="shared" si="1"/>
         <v>0.01298701299</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.014944275582573453</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
@@ -4479,6 +4637,16 @@
         <f t="shared" si="1"/>
         <v>0.005439005439</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.1523809523809524</v>
+      </c>
+      <c r="I4" s="6">
+        <f>geomean(H4:H5)</f>
+        <v>0.1551133469</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
@@ -4497,6 +4665,12 @@
         <f t="shared" si="1"/>
         <v>0.1520737327</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.15789473684210525</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
@@ -4515,6 +4689,16 @@
         <f t="shared" si="1"/>
         <v>0.004551057173</v>
       </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.132</v>
+      </c>
+      <c r="I6" s="6">
+        <f>geomean(H6:H7)</f>
+        <v>0.1267418323</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
@@ -4533,6 +4717,12 @@
         <f t="shared" si="1"/>
         <v>0.02661826981</v>
       </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.1216931216931217</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
@@ -4551,6 +4741,16 @@
         <f t="shared" si="1"/>
         <v>0.01157684631</v>
       </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.06837606837606838</v>
+      </c>
+      <c r="I8" s="6">
+        <f>geomean(H8:H9)</f>
+        <v>0.02300235027</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
@@ -4569,6 +4769,12 @@
         <f t="shared" si="1"/>
         <v>0.007885304659</v>
       </c>
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.007738206227857544</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
@@ -4587,6 +4793,16 @@
         <f t="shared" si="1"/>
         <v>0.002029220779</v>
       </c>
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="6">
+        <v>7.541478129713397E-4</v>
+      </c>
+      <c r="I10" s="6">
+        <f>geomean(H10:H11)</f>
+        <v>0.003328144529</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
@@ -4605,6 +4821,12 @@
         <f t="shared" si="1"/>
         <v>0.04090909091</v>
       </c>
+      <c r="G11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.0146875</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
@@ -4623,6 +4845,16 @@
         <f t="shared" si="1"/>
         <v>0.03866906475</v>
       </c>
+      <c r="G12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.06944444444444445</v>
+      </c>
+      <c r="I12" s="6">
+        <f>geomean(H12:H13)</f>
+        <v>0.1232516621</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
@@ -4641,6 +4873,12 @@
         <f t="shared" si="1"/>
         <v>0.06727272727</v>
       </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.21875</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
@@ -4659,6 +4897,16 @@
         <f t="shared" si="1"/>
         <v>0.002375</v>
       </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.0027111213659437015</v>
+      </c>
+      <c r="I14" s="6">
+        <f>geomean(H14:H15)</f>
+        <v>0.008725070292</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
@@ -4677,6 +4925,12 @@
         <f t="shared" si="1"/>
         <v>0.03533834586</v>
       </c>
+      <c r="G15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.0280794701986755</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
@@ -4688,12 +4942,22 @@
       <c r="C16" s="3">
         <v>102.0</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="D16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5">
         <f t="shared" si="1"/>
         <v>0.0234204793</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0.006143162393162393</v>
+      </c>
+      <c r="I16" s="6">
+        <f>geomean(H16:H17)</f>
+        <v>0.02294682498</v>
       </c>
     </row>
     <row r="17">
@@ -4706,12 +4970,18 @@
       <c r="C17" s="3">
         <v>94.0</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="D17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5">
         <f t="shared" si="1"/>
         <v>0.01494427558</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.0857142857142857</v>
       </c>
     </row>
     <row r="18">
@@ -4731,6 +5001,16 @@
         <f t="shared" si="1"/>
         <v>0.162962963</v>
       </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0.06388526727509779</v>
+      </c>
+      <c r="I18" s="6">
+        <f>geomean(H18:H19)</f>
+        <v>0.04418752492</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
@@ -4749,6 +5029,12 @@
         <f t="shared" si="1"/>
         <v>0.03175675676</v>
       </c>
+      <c r="G19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0.030563186813186816</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
@@ -5138,10 +5424,10 @@
       <c r="C41" s="3">
         <v>6.0</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="6">
+      <c r="D41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="5">
         <f t="shared" si="1"/>
         <v>0.1523809524</v>
       </c>
@@ -5156,10 +5442,10 @@
       <c r="C42" s="3">
         <v>9.0</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="6">
+      <c r="D42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="5">
         <f t="shared" si="1"/>
         <v>0.1578947368</v>
       </c>
@@ -5570,10 +5856,10 @@
       <c r="C65" s="3">
         <v>25.0</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" s="6">
+      <c r="D65" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="5">
         <f t="shared" si="1"/>
         <v>0.132</v>
       </c>
@@ -5588,10 +5874,10 @@
       <c r="C66" s="3">
         <v>7.0</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="6">
+      <c r="D66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="5">
         <f t="shared" si="1"/>
         <v>0.1216931217</v>
       </c>
@@ -5606,10 +5892,10 @@
       <c r="C67" s="3">
         <v>72.0</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="6">
+      <c r="D67" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" s="5">
         <f t="shared" si="1"/>
         <v>0.06837606838</v>
       </c>
@@ -5624,10 +5910,10 @@
       <c r="C68" s="3">
         <v>173.0</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="6">
+      <c r="D68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="5">
         <f t="shared" si="1"/>
         <v>0.007738206228</v>
       </c>
@@ -5732,10 +6018,10 @@
       <c r="C74" s="3">
         <v>34.0</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" s="6">
+      <c r="D74" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="5">
         <f t="shared" si="1"/>
         <v>0.000754147813</v>
       </c>
@@ -5750,10 +6036,10 @@
       <c r="C75" s="3">
         <v>200.0</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="6">
+      <c r="D75" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="5">
         <f t="shared" si="1"/>
         <v>0.0146875</v>
       </c>
@@ -5768,10 +6054,10 @@
       <c r="C76" s="3">
         <v>36.0</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="6">
+      <c r="D76" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="5">
         <f t="shared" si="1"/>
         <v>0.06944444444</v>
       </c>
@@ -5786,10 +6072,10 @@
       <c r="C77" s="3">
         <v>8.0</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="6">
+      <c r="D77" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="5">
         <f t="shared" si="1"/>
         <v>0.21875</v>
       </c>
@@ -5840,10 +6126,10 @@
       <c r="C80" s="3">
         <v>197.0</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E80" s="6">
+      <c r="D80" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="5">
         <f t="shared" si="1"/>
         <v>0.002711121366</v>
       </c>
@@ -5858,10 +6144,10 @@
       <c r="C81" s="3">
         <v>151.0</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="6">
+      <c r="D81" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="5">
         <f t="shared" si="1"/>
         <v>0.0280794702</v>
       </c>
@@ -6074,10 +6360,10 @@
       <c r="C93" s="3">
         <v>156.0</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E93" s="6">
+      <c r="D93" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" s="5">
         <f t="shared" si="1"/>
         <v>0.006143162393</v>
       </c>
@@ -6092,10 +6378,10 @@
       <c r="C94" s="3">
         <v>3.0</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="6">
+      <c r="D94" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="5">
         <f t="shared" si="1"/>
         <v>0.08571428571</v>
       </c>
@@ -6110,10 +6396,10 @@
       <c r="C95" s="3">
         <v>59.0</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E95" s="6">
+      <c r="D95" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="5">
         <f t="shared" si="1"/>
         <v>0.06388526728</v>
       </c>
@@ -6128,10 +6414,10 @@
       <c r="C96" s="3">
         <v>104.0</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" s="6">
+      <c r="D96" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" s="5">
         <f t="shared" si="1"/>
         <v>0.03056318681</v>
       </c>
@@ -6285,12 +6571,21 @@
         <f t="shared" ref="E2:E101" si="1">((B2/A2)-1)/C2</f>
         <v>0.000754147813</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.0010118897040222608</v>
+      </c>
+      <c r="I2" s="6">
+        <f>geomean(H2:H3)</f>
+        <v>0.001093422712</v>
+      </c>
       <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="9">
-        <f>average(E2:E101)</f>
-        <v>0.04875800789</v>
+      <c r="L2" s="11">
+        <v>0.04875800789176675</v>
       </c>
     </row>
     <row r="3">
@@ -6310,6 +6605,12 @@
         <f t="shared" si="1"/>
         <v>0.001011889704</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.0011815252416756178</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
@@ -6328,6 +6629,16 @@
         <f t="shared" si="1"/>
         <v>0.001181525242</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.004551057172655732</v>
+      </c>
+      <c r="I4" s="6">
+        <f>geomean(H4:H5)</f>
+        <v>0.004868616105</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
@@ -6346,6 +6657,12 @@
         <f t="shared" si="1"/>
         <v>0.002029220779</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.005208333333333333</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
@@ -6364,6 +6681,16 @@
         <f t="shared" si="1"/>
         <v>0.002328042328</v>
       </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.00543900543900544</v>
+      </c>
+      <c r="I6" s="6">
+        <f>geomean(H6:H7)</f>
+        <v>0.005701043219</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
@@ -6382,6 +6709,12 @@
         <f t="shared" si="1"/>
         <v>0.002375</v>
       </c>
+      <c r="G7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.005975705329153606</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
@@ -6400,6 +6733,16 @@
         <f t="shared" si="1"/>
         <v>0.002419354839</v>
       </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.006143162393162393</v>
+      </c>
+      <c r="I8" s="6">
+        <f>geomean(H8:H9)</f>
+        <v>0.006275288528</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
@@ -6418,6 +6761,12 @@
         <f t="shared" si="1"/>
         <v>0.002467105263</v>
       </c>
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.00641025641025641</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
@@ -6436,6 +6785,16 @@
         <f t="shared" si="1"/>
         <v>0.002711121366</v>
       </c>
+      <c r="G10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.006614654002713705</v>
+      </c>
+      <c r="I10" s="6">
+        <f>geomean(H10:H11)</f>
+        <v>0.006688775746</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
@@ -6454,6 +6813,12 @@
         <f t="shared" si="1"/>
         <v>0.004551057173</v>
       </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.006763728075203485</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
@@ -6472,6 +6837,16 @@
         <f t="shared" si="1"/>
         <v>0.005208333333</v>
       </c>
+      <c r="G12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.0076619718309859156</v>
+      </c>
+      <c r="I12" s="6">
+        <f>geomean(H12:H13)</f>
+        <v>0.007699994684</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
@@ -6490,6 +6865,12 @@
         <f t="shared" si="1"/>
         <v>0.005439005439</v>
       </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.007738206227857544</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
@@ -6508,6 +6889,16 @@
         <f t="shared" si="1"/>
         <v>0.005975705329</v>
       </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.007885304659498209</v>
+      </c>
+      <c r="I14" s="6">
+        <f>geomean(H14:H15)</f>
+        <v>0.008075638045</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
@@ -6526,6 +6917,12 @@
         <f t="shared" si="1"/>
         <v>0.006143162393</v>
       </c>
+      <c r="G15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0.008270565647614829</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
@@ -6544,6 +6941,16 @@
         <f t="shared" si="1"/>
         <v>0.00641025641</v>
       </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0.008447488584474886</v>
+      </c>
+      <c r="I16" s="6">
+        <f>geomean(H16:H17)</f>
+        <v>0.008530452992</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
@@ -6562,6 +6969,12 @@
         <f t="shared" si="1"/>
         <v>0.006614654003</v>
       </c>
+      <c r="G17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0.008614232209737827</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
@@ -6580,6 +6993,16 @@
         <f t="shared" si="1"/>
         <v>0.006763728075</v>
       </c>
+      <c r="G18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0.008827480330071004</v>
+      </c>
+      <c r="I18" s="6">
+        <f>geomean(H18:H19)</f>
+        <v>0.009728391541</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
@@ -6598,6 +7021,12 @@
         <f t="shared" si="1"/>
         <v>0.007661971831</v>
       </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0.010721247563352828</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
@@ -6616,6 +7045,16 @@
         <f t="shared" si="1"/>
         <v>0.007738206228</v>
       </c>
+      <c r="G20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0.011576846307385228</v>
+      </c>
+      <c r="I20" s="6">
+        <f>geomean(H20:H21)</f>
+        <v>0.01183054827</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
@@ -6634,6 +7073,12 @@
         <f t="shared" si="1"/>
         <v>0.007885304659</v>
       </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="6">
+        <v>0.012089810017271158</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
@@ -6652,6 +7097,16 @@
         <f t="shared" si="1"/>
         <v>0.008270565648</v>
       </c>
+      <c r="G22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="6">
+        <v>0.012368815592203899</v>
+      </c>
+      <c r="I22" s="6">
+        <f>geomean(H22:H23)</f>
+        <v>0.01247997707</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
@@ -6670,6 +7125,12 @@
         <f t="shared" si="1"/>
         <v>0.008447488584</v>
       </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="6">
+        <v>0.01259213759213759</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
@@ -6688,6 +7149,16 @@
         <f t="shared" si="1"/>
         <v>0.00861423221</v>
       </c>
+      <c r="G24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="6">
+        <v>0.012671232876712329</v>
+      </c>
+      <c r="I24" s="6">
+        <f>geomean(H24:H25)</f>
+        <v>0.01271923841</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
@@ -6706,6 +7177,12 @@
         <f t="shared" si="1"/>
         <v>0.008651766402</v>
       </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0.012767425810904072</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
@@ -6724,6 +7201,16 @@
         <f t="shared" si="1"/>
         <v>0.00882748033</v>
       </c>
+      <c r="G26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="6">
+        <v>0.01277089783281734</v>
+      </c>
+      <c r="I26" s="6">
+        <f>geomean(H26:H27)</f>
+        <v>0.01287850209</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
@@ -6742,6 +7229,12 @@
         <f t="shared" si="1"/>
         <v>0.01072124756</v>
       </c>
+      <c r="G27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0.012987012987012988</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
@@ -6760,6 +7253,16 @@
         <f t="shared" si="1"/>
         <v>0.01104878463</v>
       </c>
+      <c r="G28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0.014944275582573453</v>
+      </c>
+      <c r="I28" s="6">
+        <f>geomean(H28:H29)</f>
+        <v>0.01502746182</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
@@ -6778,6 +7281,12 @@
         <f t="shared" si="1"/>
         <v>0.01109307359</v>
       </c>
+      <c r="G29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0.015111111111111112</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
@@ -6796,6 +7305,16 @@
         <f t="shared" si="1"/>
         <v>0.01157684631</v>
       </c>
+      <c r="G30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0.015304921120791145</v>
+      </c>
+      <c r="I30" s="6">
+        <f>geomean(H30:H31)</f>
+        <v>0.01558100492</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
@@ -6814,6 +7333,12 @@
         <f t="shared" si="1"/>
         <v>0.01208981002</v>
       </c>
+      <c r="G31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0.015862068965517243</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
@@ -6832,6 +7357,16 @@
         <f t="shared" si="1"/>
         <v>0.01231802912</v>
       </c>
+      <c r="G32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" s="6">
+        <v>0.019607843137254905</v>
+      </c>
+      <c r="I32" s="6">
+        <f>geomean(H32:H33)</f>
+        <v>0.01988566717</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
@@ -6850,6 +7385,12 @@
         <f t="shared" si="1"/>
         <v>0.01236881559</v>
       </c>
+      <c r="G33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="6">
+        <v>0.02016742770167428</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
@@ -6868,6 +7409,16 @@
         <f t="shared" si="1"/>
         <v>0.01259213759</v>
       </c>
+      <c r="G34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="6">
+        <v>0.02019906323185012</v>
+      </c>
+      <c r="I34" s="6">
+        <f>geomean(H34:H35)</f>
+        <v>0.02110670803</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
@@ -6886,6 +7437,12 @@
         <f t="shared" si="1"/>
         <v>0.01260783013</v>
       </c>
+      <c r="G35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0.02205513784461153</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
@@ -6904,6 +7461,16 @@
         <f t="shared" si="1"/>
         <v>0.01267123288</v>
       </c>
+      <c r="G36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="6">
+        <v>0.025652985074626863</v>
+      </c>
+      <c r="I36" s="6">
+        <f>geomean(H36:H37)</f>
+        <v>0.02583508959</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
@@ -6922,6 +7489,12 @@
         <f t="shared" si="1"/>
         <v>0.01276742581</v>
       </c>
+      <c r="G37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0.026018486819582333</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
@@ -6940,6 +7513,16 @@
         <f t="shared" si="1"/>
         <v>0.01277089783</v>
       </c>
+      <c r="G38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0.030563186813186816</v>
+      </c>
+      <c r="I38" s="6">
+        <f>geomean(H38:H39)</f>
+        <v>0.03114899515</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
@@ -6958,6 +7541,12 @@
         <f t="shared" si="1"/>
         <v>0.01298701299</v>
       </c>
+      <c r="G39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0.031746031746031744</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
@@ -6976,6 +7565,16 @@
         <f t="shared" si="1"/>
         <v>0.01394759087</v>
       </c>
+      <c r="G40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H40" s="6">
+        <v>0.0857142857142857</v>
+      </c>
+      <c r="I40" s="6">
+        <f>geomean(H40:H41)</f>
+        <v>0.08666143365</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
@@ -6994,6 +7593,12 @@
         <f t="shared" si="1"/>
         <v>0.01411336217</v>
       </c>
+      <c r="G41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0.08761904761904764</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
@@ -7012,6 +7617,16 @@
         <f t="shared" si="1"/>
         <v>0.0146875</v>
       </c>
+      <c r="G42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" s="6">
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="I42" s="6">
+        <f>geomean(H42:H43)</f>
+        <v>0.1604088344</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
@@ -7029,6 +7644,12 @@
       <c r="E43" s="5">
         <f t="shared" si="1"/>
         <v>0.01494427558</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0.16296296296296298</v>
       </c>
     </row>
     <row r="44">
@@ -8088,6 +8709,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="15.13"/>
+    <col customWidth="1" min="2" max="2" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8096,38 +8718,49 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="14">
         <v>0.04875800789176675</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="6">
+    <row r="5">
+      <c r="A5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="14">
         <v>0.04875800789176675</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="6">
+    <row r="6">
+      <c r="A6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="14">
         <v>0.04875800789176677</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="6">
+    <row r="7">
+      <c r="A7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="14">
         <v>0.04875800789176675</v>
       </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>